--- a/Parquets/StretchReadiness/StretchReadiness_Output.xlsx
+++ b/Parquets/StretchReadiness/StretchReadiness_Output.xlsx
@@ -5868,7 +5868,7 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -5958,7 +5958,7 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -6048,7 +6048,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -6138,7 +6138,7 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -6228,7 +6228,7 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -6318,7 +6318,7 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -6408,7 +6408,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -6498,7 +6498,7 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -6588,7 +6588,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -6678,7 +6678,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -6768,7 +6768,7 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -6858,7 +6858,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -6948,7 +6948,7 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -7038,7 +7038,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -7128,7 +7128,7 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -7218,7 +7218,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -7308,7 +7308,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -7398,7 +7398,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -7488,7 +7488,7 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -7578,7 +7578,7 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -7668,7 +7668,7 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -7758,7 +7758,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -7848,7 +7848,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -7938,7 +7938,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -8028,7 +8028,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -8118,7 +8118,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -8208,7 +8208,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -8298,7 +8298,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -8388,7 +8388,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -8478,7 +8478,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -8568,7 +8568,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -8658,7 +8658,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -8748,7 +8748,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -8838,7 +8838,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -8928,7 +8928,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -9018,7 +9018,7 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -9108,7 +9108,7 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -9198,7 +9198,7 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -9288,7 +9288,7 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -42568,7 +42568,7 @@
       <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L517" t="n">
@@ -42658,7 +42658,7 @@
       <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -42678,7 +42678,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L518" t="n">
@@ -42748,7 +42748,7 @@
       <c r="F519" t="inlineStr"/>
       <c r="G519" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -42768,7 +42768,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L519" t="n">
@@ -42838,7 +42838,7 @@
       <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -42858,7 +42858,7 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L520" t="n">
@@ -42928,7 +42928,7 @@
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L521" t="n">
@@ -43018,7 +43018,7 @@
       <c r="F522" t="inlineStr"/>
       <c r="G522" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -43038,7 +43038,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L522" t="n">
@@ -43108,7 +43108,7 @@
       <c r="F523" t="inlineStr"/>
       <c r="G523" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -43128,7 +43128,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L523" t="n">
@@ -43198,7 +43198,7 @@
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -43218,7 +43218,7 @@
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L524" t="n">
@@ -43288,7 +43288,7 @@
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -43308,7 +43308,7 @@
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L525" t="n">
@@ -43378,7 +43378,7 @@
       <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -43398,7 +43398,7 @@
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L526" t="n">
@@ -43468,7 +43468,7 @@
       <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -43488,7 +43488,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L527" t="n">
@@ -43558,7 +43558,7 @@
       <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -43578,7 +43578,7 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L528" t="n">
@@ -43648,7 +43648,7 @@
       <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L529" t="n">
@@ -43738,7 +43738,7 @@
       <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L530" t="n">
@@ -43828,7 +43828,7 @@
       <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L531" t="n">
@@ -43918,7 +43918,7 @@
       <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -43938,7 +43938,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L532" t="n">
@@ -44008,7 +44008,7 @@
       <c r="F533" t="inlineStr"/>
       <c r="G533" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -44028,7 +44028,7 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L533" t="n">
@@ -44098,7 +44098,7 @@
       <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -44118,7 +44118,7 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L534" t="n">
@@ -44188,7 +44188,7 @@
       <c r="F535" t="inlineStr"/>
       <c r="G535" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -44208,7 +44208,7 @@
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L535" t="n">
@@ -44278,7 +44278,7 @@
       <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -44298,7 +44298,7 @@
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L536" t="n">
@@ -44368,7 +44368,7 @@
       <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L537" t="n">
@@ -44458,7 +44458,7 @@
       <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -44478,7 +44478,7 @@
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L538" t="n">
@@ -44548,7 +44548,7 @@
       <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -44568,7 +44568,7 @@
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L539" t="n">
@@ -44638,7 +44638,7 @@
       <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -44658,7 +44658,7 @@
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L540" t="n">
@@ -44728,7 +44728,7 @@
       <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L541" t="n">
@@ -44818,7 +44818,7 @@
       <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -44838,7 +44838,7 @@
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L542" t="n">
@@ -44908,7 +44908,7 @@
       <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -44928,7 +44928,7 @@
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L543" t="n">
@@ -44998,7 +44998,7 @@
       <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -45018,7 +45018,7 @@
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L544" t="n">
@@ -45088,7 +45088,7 @@
       <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -45108,7 +45108,7 @@
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L545" t="n">
@@ -45178,7 +45178,7 @@
       <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -45198,7 +45198,7 @@
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L546" t="n">
@@ -45268,7 +45268,7 @@
       <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L547" t="n">
@@ -45358,7 +45358,7 @@
       <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -45378,7 +45378,7 @@
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L548" t="n">
@@ -45448,7 +45448,7 @@
       <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -45468,7 +45468,7 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L549" t="n">
@@ -45538,7 +45538,7 @@
       <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L550" t="n">
@@ -45628,7 +45628,7 @@
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L551" t="n">
@@ -45718,7 +45718,7 @@
       <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -45738,7 +45738,7 @@
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L552" t="n">
@@ -45808,7 +45808,7 @@
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -45828,7 +45828,7 @@
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L553" t="n">
@@ -45898,7 +45898,7 @@
       <c r="F554" t="inlineStr"/>
       <c r="G554" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -45918,7 +45918,7 @@
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L554" t="n">
@@ -45988,7 +45988,7 @@
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -46008,7 +46008,7 @@
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L555" t="n">
@@ -46078,7 +46078,7 @@
       <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -46098,7 +46098,7 @@
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L556" t="n">
@@ -46168,7 +46168,7 @@
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -46188,7 +46188,7 @@
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L557" t="n">
@@ -46258,7 +46258,7 @@
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -46278,7 +46278,7 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L558" t="n">
@@ -46348,7 +46348,7 @@
       <c r="F559" t="inlineStr"/>
       <c r="G559" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L559" t="n">
@@ -46438,7 +46438,7 @@
       <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -46458,7 +46458,7 @@
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L560" t="n">
@@ -46528,7 +46528,7 @@
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -46548,7 +46548,7 @@
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L561" t="n">
@@ -46622,7 +46622,7 @@
       <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L562" t="n">
@@ -46712,7 +46712,7 @@
       <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -46732,7 +46732,7 @@
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L563" t="n">
@@ -46806,7 +46806,7 @@
       <c r="F564" t="inlineStr"/>
       <c r="G564" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -46826,7 +46826,7 @@
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L564" t="n">
@@ -46900,7 +46900,7 @@
       <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -46920,7 +46920,7 @@
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L565" t="n">
@@ -46994,7 +46994,7 @@
       <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -47014,7 +47014,7 @@
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L566" t="n">
@@ -47088,7 +47088,7 @@
       <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -47108,7 +47108,7 @@
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="L567" t="n">
@@ -62111,7 +62111,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -62249,7 +62249,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -62928,7 +62928,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -63064,7 +63064,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -64007,7 +64007,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -64069,7 +64069,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -64190,7 +64190,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -64252,7 +64252,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -65447,7 +65447,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -65498,7 +65498,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TA 418 - DPR - 2026-04-25.xlsx</t>
+          <t>TA 418 - DPR - 2026-04-29.xlsx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -65643,7 +65643,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -65694,7 +65694,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TA 421 - DPR - 2026-04-27.xlsx</t>
+          <t>TA 421 - DPR - 2026-04-28.xlsx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
